--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_EB FELIPE ANTÓN.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_EB FELIPE ANTÓN.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. NIMAGA</t>
+          <t>E. DUQUE NEGRÍN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>23.3577</v>
+        <v>40.4145</v>
       </c>
       <c r="E2" t="n">
-        <v>20.6508</v>
+        <v>62.4154</v>
       </c>
       <c r="F2" t="n">
-        <v>2.707</v>
+        <v>-22.001</v>
       </c>
       <c r="G2" t="n">
-        <v>-7.1605</v>
+        <v>16.8806</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.098700000000001</v>
+        <v>-6.1404</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.0618</v>
+        <v>23.021</v>
       </c>
       <c r="J2" t="n">
-        <v>21.4704</v>
+        <v>62.3718</v>
       </c>
       <c r="K2" t="n">
-        <v>17.5325</v>
+        <v>25.5692</v>
       </c>
       <c r="L2" t="n">
-        <v>3.9381</v>
+        <v>36.802</v>
       </c>
       <c r="M2" t="n">
-        <v>-28.6309</v>
+        <v>-45.491</v>
       </c>
       <c r="N2" t="n">
-        <v>-18.6314</v>
+        <v>-31.7099</v>
       </c>
       <c r="O2" t="n">
-        <v>-9.999500000000001</v>
+        <v>-13.7814</v>
       </c>
       <c r="P2" t="n">
-        <v>-7.1793</v>
+        <v>11.2539</v>
       </c>
       <c r="Q2" t="n">
-        <v>-44.6275</v>
+        <v>-39.3886</v>
       </c>
       <c r="R2" t="n">
-        <v>37.4483</v>
+        <v>50.6423</v>
       </c>
       <c r="S2" t="n">
-        <v>37.2723</v>
+        <v>-4.8639</v>
       </c>
       <c r="T2" t="n">
-        <v>27.7198</v>
+        <v>-0.3823000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>9.5524</v>
+        <v>-4.4815</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4254</v>
+        <v>17.1438</v>
       </c>
       <c r="W2" t="n">
-        <v>16.0879</v>
+        <v>39.8148</v>
       </c>
       <c r="X2" t="n">
-        <v>-15.6624</v>
+        <v>-22.6708</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. DUQUE NEGRÍN</t>
+          <t>K. RIVEROL DE LAS CASAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>21.2232</v>
+        <v>23.1693</v>
       </c>
       <c r="E3" t="n">
-        <v>47.3115</v>
+        <v>41.7552</v>
       </c>
       <c r="F3" t="n">
-        <v>-26.0885</v>
+        <v>-18.5854</v>
       </c>
       <c r="G3" t="n">
-        <v>16.8806</v>
+        <v>2.1025</v>
       </c>
       <c r="H3" t="n">
-        <v>-6.1404</v>
+        <v>-8.387799999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>23.021</v>
+        <v>10.4903</v>
       </c>
       <c r="J3" t="n">
-        <v>62.3718</v>
+        <v>38.7136</v>
       </c>
       <c r="K3" t="n">
-        <v>25.5692</v>
+        <v>18.8461</v>
       </c>
       <c r="L3" t="n">
-        <v>36.802</v>
+        <v>19.8677</v>
       </c>
       <c r="M3" t="n">
-        <v>-45.491</v>
+        <v>-36.6112</v>
       </c>
       <c r="N3" t="n">
-        <v>-31.7099</v>
+        <v>-27.2343</v>
       </c>
       <c r="O3" t="n">
-        <v>-13.7814</v>
+        <v>-9.376799999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>11.2539</v>
+        <v>12.2243</v>
       </c>
       <c r="Q3" t="n">
-        <v>-39.3886</v>
+        <v>-32.4035</v>
       </c>
       <c r="R3" t="n">
-        <v>50.6423</v>
+        <v>44.6278</v>
       </c>
       <c r="S3" t="n">
-        <v>-24.0553</v>
+        <v>-6.0045</v>
       </c>
       <c r="T3" t="n">
-        <v>-15.4864</v>
+        <v>0.2389000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-8.569000000000001</v>
+        <v>-6.2432</v>
       </c>
       <c r="V3" t="n">
-        <v>17.1438</v>
+        <v>14.847</v>
       </c>
       <c r="W3" t="n">
-        <v>39.8148</v>
+        <v>35.2057</v>
       </c>
       <c r="X3" t="n">
-        <v>-22.6708</v>
+        <v>-20.3587</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. FERNANDEZ SHEPHARD</t>
+          <t>J. GALLETTO LAMELA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>13.9703</v>
+        <v>10.8629</v>
       </c>
       <c r="E4" t="n">
-        <v>29.8942</v>
+        <v>8.8947</v>
       </c>
       <c r="F4" t="n">
-        <v>-15.9241</v>
+        <v>1.9682</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1409</v>
+        <v>34.991</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3585</v>
+        <v>18.0613</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4992</v>
+        <v>16.9302</v>
       </c>
       <c r="J4" t="n">
-        <v>26.3017</v>
+        <v>60.1917</v>
       </c>
       <c r="K4" t="n">
-        <v>15.9958</v>
+        <v>40.4858</v>
       </c>
       <c r="L4" t="n">
-        <v>10.3059</v>
+        <v>19.706</v>
       </c>
       <c r="M4" t="n">
-        <v>-23.161</v>
+        <v>-25.2002</v>
       </c>
       <c r="N4" t="n">
-        <v>-17.3545</v>
+        <v>-22.4246</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.8064</v>
+        <v>-2.776</v>
       </c>
       <c r="P4" t="n">
-        <v>6.4031</v>
+        <v>-28.3287</v>
       </c>
       <c r="Q4" t="n">
-        <v>-28.5228</v>
+        <v>-71.2099</v>
       </c>
       <c r="R4" t="n">
-        <v>34.9261</v>
+        <v>42.8813</v>
       </c>
       <c r="S4" t="n">
-        <v>7.620099999999999</v>
+        <v>-3.7244</v>
       </c>
       <c r="T4" t="n">
-        <v>10.09</v>
+        <v>-3.0495</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.4699</v>
+        <v>-0.6752999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-3.194</v>
+        <v>7.924299999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>22.0253</v>
+        <v>22.9624</v>
       </c>
       <c r="X4" t="n">
-        <v>-25.2192</v>
+        <v>-15.0378</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. RIVEROL DE LAS CASAS</t>
+          <t>B. FERNANDEZ SHEPHARD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>9.908300000000001</v>
+        <v>7.3316</v>
       </c>
       <c r="E5" t="n">
-        <v>32.8572</v>
+        <v>22.9343</v>
       </c>
       <c r="F5" t="n">
-        <v>-22.9481</v>
+        <v>-15.6024</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1025</v>
+        <v>3.1409</v>
       </c>
       <c r="H5" t="n">
-        <v>-8.387799999999999</v>
+        <v>-1.3585</v>
       </c>
       <c r="I5" t="n">
-        <v>10.4903</v>
+        <v>4.4992</v>
       </c>
       <c r="J5" t="n">
-        <v>38.7136</v>
+        <v>26.3017</v>
       </c>
       <c r="K5" t="n">
-        <v>18.8461</v>
+        <v>15.9958</v>
       </c>
       <c r="L5" t="n">
-        <v>19.8677</v>
+        <v>10.3059</v>
       </c>
       <c r="M5" t="n">
-        <v>-36.6112</v>
+        <v>-23.161</v>
       </c>
       <c r="N5" t="n">
-        <v>-27.2343</v>
+        <v>-17.3545</v>
       </c>
       <c r="O5" t="n">
-        <v>-9.376799999999999</v>
+        <v>-5.8064</v>
       </c>
       <c r="P5" t="n">
-        <v>12.2243</v>
+        <v>6.4031</v>
       </c>
       <c r="Q5" t="n">
-        <v>-32.4035</v>
+        <v>-28.5228</v>
       </c>
       <c r="R5" t="n">
-        <v>44.6278</v>
+        <v>34.9261</v>
       </c>
       <c r="S5" t="n">
-        <v>-19.2655</v>
+        <v>0.9818999999999998</v>
       </c>
       <c r="T5" t="n">
-        <v>-8.659000000000001</v>
+        <v>3.1302</v>
       </c>
       <c r="U5" t="n">
-        <v>-10.6059</v>
+        <v>-2.1485</v>
       </c>
       <c r="V5" t="n">
-        <v>14.847</v>
+        <v>-3.194</v>
       </c>
       <c r="W5" t="n">
-        <v>35.2057</v>
+        <v>22.0253</v>
       </c>
       <c r="X5" t="n">
-        <v>-20.3587</v>
+        <v>-25.2192</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. MANERO GUZMAN</t>
+          <t>L. GIFREU LLARCH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>5.9872</v>
+        <v>4.474200000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>13.2242</v>
+        <v>3.633400000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-7.237100000000002</v>
+        <v>0.8406999999999998</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.538599999999999</v>
+        <v>2.2233</v>
       </c>
       <c r="H6" t="n">
-        <v>-10.2412</v>
+        <v>-4.7883</v>
       </c>
       <c r="I6" t="n">
-        <v>5.702899999999999</v>
+        <v>7.0115</v>
       </c>
       <c r="J6" t="n">
-        <v>33.7736</v>
+        <v>9.296900000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>19.0606</v>
+        <v>0.9393</v>
       </c>
       <c r="L6" t="n">
-        <v>14.7129</v>
+        <v>8.3575</v>
       </c>
       <c r="M6" t="n">
-        <v>-38.3122</v>
+        <v>-7.0737</v>
       </c>
       <c r="N6" t="n">
-        <v>-29.3022</v>
+        <v>-5.7276</v>
       </c>
       <c r="O6" t="n">
-        <v>-9.0099</v>
+        <v>-1.3461</v>
       </c>
       <c r="P6" t="n">
-        <v>6.597199999999999</v>
+        <v>-7.3732</v>
       </c>
       <c r="Q6" t="n">
-        <v>-44.6276</v>
+        <v>-20.7615</v>
       </c>
       <c r="R6" t="n">
-        <v>51.2245</v>
+        <v>13.3883</v>
       </c>
       <c r="S6" t="n">
-        <v>19.0769</v>
+        <v>3.3824</v>
       </c>
       <c r="T6" t="n">
-        <v>12.0301</v>
+        <v>2.4384</v>
       </c>
       <c r="U6" t="n">
-        <v>7.0466</v>
+        <v>0.9439000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-15.1487</v>
+        <v>6.2418</v>
       </c>
       <c r="W6" t="n">
-        <v>12.0477</v>
+        <v>12.6596</v>
       </c>
       <c r="X6" t="n">
-        <v>-27.1963</v>
+        <v>-6.4178</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. GIFREU LLARCH</t>
+          <t>A. SISTAC RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>4.9526</v>
+        <v>0.9340000000000003</v>
       </c>
       <c r="E7" t="n">
-        <v>4.152499999999999</v>
+        <v>3.7242</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8002999999999998</v>
+        <v>-2.7902</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2233</v>
+        <v>-9.7415</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.7883</v>
+        <v>-15.8545</v>
       </c>
       <c r="I7" t="n">
-        <v>7.0115</v>
+        <v>6.113199999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>9.296900000000001</v>
+        <v>25.514</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9393</v>
+        <v>11.164</v>
       </c>
       <c r="L7" t="n">
-        <v>8.3575</v>
+        <v>14.3503</v>
       </c>
       <c r="M7" t="n">
-        <v>-7.0737</v>
+        <v>-35.2554</v>
       </c>
       <c r="N7" t="n">
-        <v>-5.7276</v>
+        <v>-27.0187</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3461</v>
+        <v>-8.236800000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-7.3732</v>
+        <v>19.7913</v>
       </c>
       <c r="Q7" t="n">
-        <v>-20.7615</v>
+        <v>-32.5974</v>
       </c>
       <c r="R7" t="n">
-        <v>13.3883</v>
+        <v>52.3888</v>
       </c>
       <c r="S7" t="n">
-        <v>3.8609</v>
+        <v>-6.6197</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9573</v>
+        <v>-2.646</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9035</v>
+        <v>-3.9735</v>
       </c>
       <c r="V7" t="n">
-        <v>6.2418</v>
+        <v>-2.4965</v>
       </c>
       <c r="W7" t="n">
-        <v>12.6596</v>
+        <v>13.4538</v>
       </c>
       <c r="X7" t="n">
-        <v>-6.4178</v>
+        <v>-15.9499</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GALLETTO LAMELA</t>
+          <t>M. NIMAGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5925999999999991</v>
+        <v>-0.6721999999999995</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6012000000000013</v>
+        <v>2.458699999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008299999999999697</v>
+        <v>-3.131</v>
       </c>
       <c r="G8" t="n">
-        <v>34.991</v>
+        <v>-7.1605</v>
       </c>
       <c r="H8" t="n">
-        <v>18.0613</v>
+        <v>-1.098700000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>16.9302</v>
+        <v>-6.0618</v>
       </c>
       <c r="J8" t="n">
-        <v>60.1917</v>
+        <v>21.4704</v>
       </c>
       <c r="K8" t="n">
-        <v>40.4858</v>
+        <v>17.5325</v>
       </c>
       <c r="L8" t="n">
-        <v>19.706</v>
+        <v>3.9381</v>
       </c>
       <c r="M8" t="n">
-        <v>-25.2002</v>
+        <v>-28.6309</v>
       </c>
       <c r="N8" t="n">
-        <v>-22.4246</v>
+        <v>-18.6314</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.776</v>
+        <v>-9.999500000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-28.3287</v>
+        <v>-7.1793</v>
       </c>
       <c r="Q8" t="n">
-        <v>-71.2099</v>
+        <v>-44.6275</v>
       </c>
       <c r="R8" t="n">
-        <v>42.8813</v>
+        <v>37.4483</v>
       </c>
       <c r="S8" t="n">
-        <v>-15.18</v>
+        <v>13.2423</v>
       </c>
       <c r="T8" t="n">
-        <v>-12.5456</v>
+        <v>9.527800000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.6348</v>
+        <v>3.7142</v>
       </c>
       <c r="V8" t="n">
-        <v>7.924299999999999</v>
+        <v>0.4254</v>
       </c>
       <c r="W8" t="n">
-        <v>22.9624</v>
+        <v>16.0879</v>
       </c>
       <c r="X8" t="n">
-        <v>-15.0378</v>
+        <v>-15.6624</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. PÉREZ DE PAIZ</t>
+          <t>J. JIMENEZ BARNÉS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9371</v>
+        <v>-0.7010999999999996</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7885</v>
+        <v>-0.9182000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1486</v>
+        <v>0.2172999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4004</v>
+        <v>-0.7211</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4004</v>
+        <v>0.1318</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0.8530000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6673</v>
+        <v>-0.4758000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6673</v>
+        <v>0.0824</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.5581999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2669</v>
+        <v>-0.2452999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2669</v>
+        <v>0.04940000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.2948</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.9702</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2546</v>
+        <v>-0.0275</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1211</v>
+        <v>-0.08410000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1335</v>
+        <v>0.0566</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2821</v>
+        <v>0.04769999999999996</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2821</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. JIMENEZ BARNÉS</t>
+          <t>I. PÉREZ DE PAIZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3587</v>
+        <v>-0.9371</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4398</v>
+        <v>-0.7885</v>
       </c>
       <c r="F10" t="n">
-        <v>0.08100000000000007</v>
+        <v>-0.1486</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7211</v>
+        <v>-0.4004</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1318</v>
+        <v>-0.4004</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8530000000000001</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4758000000000001</v>
+        <v>-0.6673</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0824</v>
+        <v>-0.6673</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5581999999999999</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2452999999999999</v>
+        <v>0.2669</v>
       </c>
       <c r="N10" t="n">
-        <v>0.04940000000000001</v>
+        <v>0.2669</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2948</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9702</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6852</v>
+        <v>-0.2546</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6056</v>
+        <v>-0.1211</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0796</v>
+        <v>-0.1335</v>
       </c>
       <c r="V10" t="n">
-        <v>0.04769999999999996</v>
+        <v>-0.2821</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5642</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4752</v>
+        <v>-1.1777</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9791</v>
+        <v>-1.5181</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5039</v>
+        <v>0.3404</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1475</v>
@@ -1312,13 +1312,13 @@
         <v>0.9702</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3277</v>
+        <v>-0.0303</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.424</v>
+        <v>0.037</v>
       </c>
       <c r="U11" t="n">
-        <v>0.09619999999999999</v>
+        <v>-0.0673</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8286</v>
+        <v>-2.3558</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2333</v>
+        <v>-1.0331</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5953</v>
+        <v>-1.3228</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5274</v>
@@ -1390,13 +1390,13 @@
         <v>1.1641</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8973</v>
+        <v>-0.4245</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.848</v>
+        <v>-0.6477999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.04930000000000001</v>
+        <v>0.2232</v>
       </c>
       <c r="V12" t="n">
         <v>-1.374</v>
@@ -1423,13 +1423,13 @@
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.6583</v>
+        <v>-3.513100000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.4073</v>
+        <v>-2.185999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.251</v>
+        <v>-1.3272</v>
       </c>
       <c r="G13" t="n">
         <v>-2.2074</v>
@@ -1468,13 +1468,13 @@
         <v>6.7911</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.9091</v>
+        <v>-0.764</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5025000000000002</v>
+        <v>-0.2813</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.4065</v>
+        <v>-0.4827</v>
       </c>
       <c r="V13" t="n">
         <v>1.0105</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. SISTAC RODRIGUEZ</t>
+          <t>S. MANERO GUZMAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.263800000000002</v>
+        <v>-4.447699999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.0703</v>
+        <v>5.924499999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.1938</v>
+        <v>-10.3724</v>
       </c>
       <c r="G14" t="n">
-        <v>-9.7415</v>
+        <v>-4.538599999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-15.8545</v>
+        <v>-10.2412</v>
       </c>
       <c r="I14" t="n">
-        <v>6.113199999999999</v>
+        <v>5.702899999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>25.514</v>
+        <v>33.7736</v>
       </c>
       <c r="K14" t="n">
-        <v>11.164</v>
+        <v>19.0606</v>
       </c>
       <c r="L14" t="n">
-        <v>14.3503</v>
+        <v>14.7129</v>
       </c>
       <c r="M14" t="n">
-        <v>-35.2554</v>
+        <v>-38.3122</v>
       </c>
       <c r="N14" t="n">
-        <v>-27.0187</v>
+        <v>-29.3022</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.236800000000001</v>
+        <v>-9.0099</v>
       </c>
       <c r="P14" t="n">
-        <v>19.7913</v>
+        <v>6.597199999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-32.5974</v>
+        <v>-44.6276</v>
       </c>
       <c r="R14" t="n">
-        <v>52.3888</v>
+        <v>51.2245</v>
       </c>
       <c r="S14" t="n">
-        <v>-16.817</v>
+        <v>8.6424</v>
       </c>
       <c r="T14" t="n">
-        <v>-10.4404</v>
+        <v>4.7305</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.3768</v>
+        <v>3.9116</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.4965</v>
+        <v>-15.1487</v>
       </c>
       <c r="W14" t="n">
-        <v>13.4538</v>
+        <v>12.0477</v>
       </c>
       <c r="X14" t="n">
-        <v>-15.9499</v>
+        <v>-27.1963</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>-19.7036</v>
+        <v>-17.27</v>
       </c>
       <c r="E15" t="n">
-        <v>-14.8713</v>
+        <v>-13.8492</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.8323</v>
+        <v>-3.4206</v>
       </c>
       <c r="G15" t="n">
         <v>-6.3752</v>
@@ -1624,13 +1624,13 @@
         <v>6.985</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.5586</v>
+        <v>-2.1253</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.4317</v>
+        <v>-1.4097</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.1272</v>
+        <v>-0.7154</v>
       </c>
       <c r="V15" t="n">
         <v>-5.6654</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. KHIVRENKO</t>
+          <t>P. ARGÜELLES ELORZA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-27.0576</v>
+        <v>-23.1355</v>
       </c>
       <c r="E16" t="n">
-        <v>-14.3288</v>
+        <v>3.135100000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-12.7287</v>
+        <v>-26.2703</v>
       </c>
       <c r="G16" t="n">
-        <v>-13.9996</v>
+        <v>-22.4352</v>
       </c>
       <c r="H16" t="n">
-        <v>-16.6733</v>
+        <v>-18.5579</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6739</v>
+        <v>-3.8773</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3002</v>
+        <v>9.4194</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.8813999999999996</v>
+        <v>5.5491</v>
       </c>
       <c r="L16" t="n">
-        <v>4.1816</v>
+        <v>3.8703</v>
       </c>
       <c r="M16" t="n">
-        <v>-17.3</v>
+        <v>-31.8544</v>
       </c>
       <c r="N16" t="n">
-        <v>-15.7924</v>
+        <v>-24.1072</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.5073</v>
+        <v>-7.7474</v>
       </c>
       <c r="P16" t="n">
-        <v>-13.5821</v>
+        <v>8.7315</v>
       </c>
       <c r="Q16" t="n">
-        <v>-38.6125</v>
+        <v>-30.2693</v>
       </c>
       <c r="R16" t="n">
-        <v>25.0303</v>
+        <v>39.00069999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>9.584</v>
+        <v>-5.1667</v>
       </c>
       <c r="T16" t="n">
-        <v>12.7506</v>
+        <v>-1.2388</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.1665</v>
+        <v>-3.9278</v>
       </c>
       <c r="V16" t="n">
-        <v>-9.059899999999999</v>
+        <v>-4.264900000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>8.232800000000001</v>
+        <v>25.2236</v>
       </c>
       <c r="X16" t="n">
-        <v>-17.2926</v>
+        <v>-29.4885</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. ARGÜELLES ELORZA</t>
+          <t>M. KHIVRENKO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>-31.5538</v>
+        <v>-36.1549</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.5371</v>
+        <v>-23.5723</v>
       </c>
       <c r="F17" t="n">
-        <v>-28.0171</v>
+        <v>-12.5819</v>
       </c>
       <c r="G17" t="n">
-        <v>-22.4352</v>
+        <v>-13.9996</v>
       </c>
       <c r="H17" t="n">
-        <v>-18.5579</v>
+        <v>-16.6733</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.8773</v>
+        <v>2.6739</v>
       </c>
       <c r="J17" t="n">
-        <v>9.4194</v>
+        <v>3.3002</v>
       </c>
       <c r="K17" t="n">
-        <v>5.5491</v>
+        <v>-0.8813999999999996</v>
       </c>
       <c r="L17" t="n">
-        <v>3.8703</v>
+        <v>4.1816</v>
       </c>
       <c r="M17" t="n">
-        <v>-31.8544</v>
+        <v>-17.3</v>
       </c>
       <c r="N17" t="n">
-        <v>-24.1072</v>
+        <v>-15.7924</v>
       </c>
       <c r="O17" t="n">
-        <v>-7.7474</v>
+        <v>-1.5073</v>
       </c>
       <c r="P17" t="n">
-        <v>8.7315</v>
+        <v>-13.5821</v>
       </c>
       <c r="Q17" t="n">
-        <v>-30.2693</v>
+        <v>-38.6125</v>
       </c>
       <c r="R17" t="n">
-        <v>39.00069999999999</v>
+        <v>25.0303</v>
       </c>
       <c r="S17" t="n">
-        <v>-13.5854</v>
+        <v>0.4873000000000003</v>
       </c>
       <c r="T17" t="n">
-        <v>-7.9111</v>
+        <v>3.507</v>
       </c>
       <c r="U17" t="n">
-        <v>-5.6746</v>
+        <v>-3.0197</v>
       </c>
       <c r="V17" t="n">
-        <v>-4.264900000000001</v>
+        <v>-9.059899999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>25.2236</v>
+        <v>8.232800000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>-29.4885</v>
+        <v>-17.2926</v>
       </c>
     </row>
     <row r="18">
@@ -1813,19 +1813,19 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>-20.03</v>
+        <v>-3.178599999999989</v>
       </c>
       <c r="E18" t="n">
-        <v>102.8337</v>
+        <v>111.0101</v>
       </c>
       <c r="F18" t="n">
-        <v>-122.8641</v>
+        <v>-114.1872</v>
       </c>
       <c r="G18" t="n">
         <v>-10.9161</v>
       </c>
       <c r="H18" t="n">
-        <v>-67.33370000000001</v>
+        <v>-67.33369999999999</v>
       </c>
       <c r="I18" t="n">
         <v>56.4187</v>
@@ -1849,7 +1849,7 @@
         <v>-70.60550000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>4.851300000000005</v>
+        <v>4.851300000000004</v>
       </c>
       <c r="Q18" t="n">
         <v>-403.5881</v>
@@ -1858,16 +1858,16 @@
         <v>408.439</v>
       </c>
       <c r="S18" t="n">
-        <v>-20.1215</v>
+        <v>-3.269100000000002</v>
       </c>
       <c r="T18" t="n">
-        <v>5.572399999999999</v>
+        <v>13.7492</v>
       </c>
       <c r="U18" t="n">
-        <v>-25.6949</v>
+        <v>-17.0189</v>
       </c>
       <c r="V18" t="n">
-        <v>6.154999999999998</v>
+        <v>6.155000000000001</v>
       </c>
       <c r="W18" t="n">
         <v>215.009</v>
